--- a/config/tables/gas.effect.xlsx
+++ b/config/tables/gas.effect.xlsx
@@ -1,144 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Bevy\BevyProjects\bevy_gas\config\tables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11775"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Effect" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effect" sheetId="1" r:id="Rbe25a3cebadd4816"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>duration_kind</t>
-  </si>
-  <si>
-    <t>duration_ticks</t>
-  </si>
-  <si>
-    <t>period_ticks</t>
-  </si>
-  <si>
-    <t>execute_on_applied</t>
-  </si>
-  <si>
-    <t>probability</t>
-  </si>
-  <si>
-    <t>asset_tags</t>
-  </si>
-  <si>
-    <t>granted_tags</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int#range=[1,1000000]</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>gas.DurationKind</t>
-  </si>
-  <si>
-    <t>int?#range=[1,1000000]</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>float#range=[0,1]</t>
-  </si>
-  <si>
-    <t>(list#sep=;),string#ref=gas.TbTag</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>Unique effect identifier.</t>
-  </si>
-  <si>
-    <t>Designer effect name.</t>
-  </si>
-  <si>
-    <t>Instant, finite ticks, or infinite lifetime.</t>
-  </si>
-  <si>
-    <t>Lifetime in fixed ticks. Required only for DurationTicks.</t>
-  </si>
-  <si>
-    <t>Execution period in fixed ticks. Blank disables periodic execution.</t>
-  </si>
-  <si>
-    <t>Execute the periodic effect immediately on application.</t>
-  </si>
-  <si>
-    <t>Application probability from zero to one.</t>
-  </si>
-  <si>
-    <t>Effect identity tags separated by semicolons.</t>
-  </si>
-  <si>
-    <t>Tags granted while active, separated by semicolons.</t>
-  </si>
-  <si>
-    <t>Fireball mana cost</t>
-  </si>
-  <si>
-    <t>Instant</t>
-  </si>
-  <si>
-    <t>Fireball cooldown</t>
-  </si>
-  <si>
-    <t>DurationTicks</t>
-  </si>
-  <si>
-    <t>Cooldown.Fireball</t>
-  </si>
-  <si>
-    <t>Fireball damage</t>
-  </si>
-</sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t xml:space="preserve">##var</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">name</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">duration_kind</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">duration_ticks</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">period_ticks</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">execute_on_applied</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">probability</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">asset_tags</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">granted_tags</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">##type</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">int#range=[1,1000000]</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">string</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">gas.DurationKind</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">int?#range=[1,1000000]</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">float#range=[0,1]</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(list#sep=;),string#ref=gas.TbTag</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">##group</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">##</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Unique effect identifier.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Designer effect name.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Instant, finite ticks, or infinite lifetime.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Lifetime in fixed ticks. Required only for DurationTicks.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Execution period in fixed ticks. Blank disables periodic execution.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Execute the periodic effect immediately on application.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Application probability from zero to one.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Effect identity tags separated by semicolons.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tags granted while active, separated by semicolons.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fireball mana cost</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Instant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fireball cooldown</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">DurationTicks</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cooldown.Fireball</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fireball damage</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1280,211 +1256,225 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="10" width="23" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" ht="52" customHeight="1" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1" spans="1:10">
-      <c r="A3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" ht="66" customHeight="1" spans="1:10">
-      <c r="A4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1" spans="1:10">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6">
-        <v>2001</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8">
-        <v>1</v>
-      </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-    </row>
-    <row r="6" ht="40" customHeight="1" spans="1:10">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6">
-        <v>2002</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="6">
-        <v>180</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>1</v>
-      </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1" spans="1:10">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6">
-        <v>2003</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>1</v>
-      </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="D5:D7">
-      <formula1>"Instant,DurationTicks,Infinite"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="G5:G7">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" customWidth="1"/>
+    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="3" max="10" width="23" customWidth="1"/>
+    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K1" t="str" s="1">
+        <x:v>modifier_ids</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="52" customHeight="1">
+      <x:c r="A2" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K2" t="str" s="2">
+        <x:v>(list#sep=;),(int#ref=gas.TbModifier)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="25" customHeight="1">
+      <x:c r="A3" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B3" s="3"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="3"/>
+      <x:c r="I3" s="3"/>
+      <x:c r="J3" s="3"/>
+      <x:c r="K3" s="3"/>
+    </x:row>
+    <x:row r="4" ht="66" customHeight="1">
+      <x:c r="A4" s="4" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G4" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H4" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I4" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J4" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K4" t="str" s="4">
+        <x:v>Modifier IDs in application order. Blank means none.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="40" customHeight="1">
+      <x:c r="A5" s="5"/>
+      <x:c r="B5" s="6">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E5" s="6"/>
+      <x:c r="F5" s="6"/>
+      <x:c r="G5" s="5" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I5" s="7"/>
+      <x:c r="J5" s="7"/>
+      <x:c r="K5" t="str" s="7">
+        <x:v>20101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="40" customHeight="1">
+      <x:c r="A6" s="5"/>
+      <x:c r="B6" s="6">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E6" s="6">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F6" s="6"/>
+      <x:c r="G6" s="5" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I6" s="7"/>
+      <x:c r="J6" s="7" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K6" s="7"/>
+    </x:row>
+    <x:row r="7" ht="40" customHeight="1">
+      <x:c r="A7" s="5"/>
+      <x:c r="B7" s="6">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E7" s="6"/>
+      <x:c r="F7" s="6"/>
+      <x:c r="G7" s="5" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I7" s="7"/>
+      <x:c r="J7" s="7"/>
+      <x:c r="K7" t="str" s="7">
+        <x:v>20301</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="D5:D7">
+      <x:formula1>"Instant,DurationTicks,Infinite"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G5:G7">
+      <x:formula1>"TRUE,FALSE"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>